--- a/muza/weekly-promo-spend/muza_promo_spend_20260817_20260823.xlsx
+++ b/muza/weekly-promo-spend/muza_promo_spend_20260817_20260823.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,7 +744,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1350,16 +1350,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>412639</v>
+        <v>5362696</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Європіано</t>
+          <t>Муза</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Молодіжна</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1368,30 +1368,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>502633</v>
+        <v>412639</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчилля</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1409,30 +1409,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>652646</v>
+        <v>502633</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Вінстона Черчилля</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1473,7 +1473,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>802633</v>
+        <v>652646</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>вул. Героїв полку «Азов»</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1491,30 +1491,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2898</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>982639</v>
+        <v>802633</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1532,65 +1532,106 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2898</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>982639</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Європіано</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>вул. Саксаганського</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>1012643</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Європіано</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>вул. Бастіонна</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Kyiv</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Kyiv</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,11 +1709,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SVIVX</t>
+          <t>SULLR</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>326124234</v>
+        <v>326156536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1681,25 +1722,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1286</v>
+        <v>635</v>
       </c>
       <c r="H2" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="J2" t="n">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -1710,11 +1751,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8C9E2</t>
+          <t>RASPV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>326141475</v>
+        <v>326160946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1723,7 +1764,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1732,16 +1773,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>570</v>
+        <v>1047</v>
       </c>
       <c r="H3" t="n">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J3" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -1752,11 +1793,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Z2W1A</t>
+          <t>WKK2M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>326175314</v>
+        <v>326170966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1765,25 +1806,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>776</v>
+        <v>825</v>
       </c>
       <c r="H4" t="n">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="I4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>62</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
@@ -1794,11 +1835,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E98NJ</t>
+          <t>EOHN7</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>326187954</v>
+        <v>326220564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1807,7 +1848,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Вінстона Черчиля</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1816,16 +1857,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>705</v>
+        <v>1058</v>
       </c>
       <c r="H5" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -1836,11 +1877,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PUPBI</t>
+          <t>ZHQPI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>326216591</v>
+        <v>326186294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1849,7 +1890,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1858,16 +1899,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>670</v>
+        <v>1411</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -1878,11 +1919,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KBASA</t>
+          <t>6UHJJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>326116108</v>
+        <v>326170109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1891,25 +1932,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>978</v>
+        <v>923</v>
       </c>
       <c r="H7" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="J7" t="n">
-        <v>149</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1920,11 +1961,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BN5SD</t>
+          <t>DDJHB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>326116606</v>
+        <v>326248685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1933,25 +1974,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>436</v>
+        <v>1230</v>
       </c>
       <c r="H8" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="J8" t="n">
-        <v>48</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
@@ -2004,11 +2045,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DNFJA</t>
+          <t>W57XM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>326178102</v>
+        <v>326219468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2017,7 +2058,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2026,16 +2067,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>538</v>
+        <v>875</v>
       </c>
       <c r="H10" t="n">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -2046,11 +2087,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0L7OC</t>
+          <t>YNX6X</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>326187847</v>
+        <v>326207106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2059,7 +2100,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2068,16 +2109,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>832</v>
+        <v>678</v>
       </c>
       <c r="H11" t="n">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>140</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -2088,11 +2129,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VKR08</t>
+          <t>0L7OC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>326262272</v>
+        <v>326187847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2110,16 +2151,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>896</v>
+        <v>832</v>
       </c>
       <c r="H12" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="I12" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2130,11 +2171,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EOHN7</t>
+          <t>EP1J1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>326220564</v>
+        <v>326124322</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2143,7 +2184,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчиля</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2152,16 +2193,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1058</v>
+        <v>541</v>
       </c>
       <c r="H13" t="n">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>129</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -2172,11 +2213,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>YUOBP</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>326236427</v>
+        <v>326192427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2226,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчиля</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2194,16 +2235,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>862</v>
+        <v>568</v>
       </c>
       <c r="H14" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J14" t="n">
-        <v>135</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -2214,11 +2255,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0N35U</t>
+          <t>SVIVX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>326130893</v>
+        <v>326124234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2227,7 +2268,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2236,16 +2277,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>887</v>
+        <v>1286</v>
       </c>
       <c r="H15" t="n">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="J15" t="n">
-        <v>154</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">
@@ -2256,11 +2297,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZHQPI</t>
+          <t>O7EBF</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>326186294</v>
+        <v>326163252</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,25 +2310,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1411</v>
+        <v>567</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -2298,11 +2339,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E8TJX</t>
+          <t>DNFJA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>326255976</v>
+        <v>326178102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,7 +2352,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2320,31 +2361,31 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="H17" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>YUOBP</t>
+          <t>YC61U</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>326192427</v>
+        <v>326977076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,40 +2394,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>568</v>
+        <v>986</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>YNX6X</t>
+          <t>OFJI6</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>326207106</v>
+        <v>326961338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,7 +2436,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2404,31 +2445,31 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>678</v>
+        <v>1148</v>
       </c>
       <c r="H19" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SB6QE</t>
+          <t>A0BVY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>326246119</v>
+        <v>326994940</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,7 +2478,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2446,31 +2487,31 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="H20" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6UHJJ</t>
+          <t>0ZFDW</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>326170109</v>
+        <v>326972974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2479,40 +2520,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>923</v>
+        <v>1828</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>50</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EP1J1</t>
+          <t>7MYE5</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>326124322</v>
+        <v>327069057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2521,40 +2562,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>541</v>
+        <v>1314</v>
       </c>
       <c r="H22" t="n">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>41</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RASPV</t>
+          <t>TUAP4</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>326160946</v>
+        <v>327001613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2563,7 +2604,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2572,31 +2613,31 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1047</v>
+        <v>729</v>
       </c>
       <c r="H23" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I23" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>YTLJ1</t>
+          <t>LMP88</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>326208615</v>
+        <v>327083950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2605,7 +2646,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2614,31 +2655,31 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>655</v>
+        <v>1261</v>
       </c>
       <c r="H24" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>129</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>W57XM</t>
+          <t>W5ZDC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>326219468</v>
+        <v>327043373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2647,7 +2688,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2656,31 +2697,31 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>875</v>
+        <v>2079</v>
       </c>
       <c r="H25" t="n">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>116</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KSOM5</t>
+          <t>08AYA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>326232732</v>
+        <v>327003469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2689,7 +2730,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2698,31 +2739,31 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1205</v>
+        <v>1345</v>
       </c>
       <c r="H26" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PIV31</t>
+          <t>1AUE9</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>326127631</v>
+        <v>327051488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2731,40 +2772,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1030</v>
+        <v>538</v>
       </c>
       <c r="H27" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="I27" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>143</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SULLR</t>
+          <t>KDZDR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>326156536</v>
+        <v>326755831</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2773,40 +2814,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>635</v>
+        <v>2008</v>
       </c>
       <c r="H28" t="n">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="I28" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>113</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>00JZX</t>
+          <t>55HJ4</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>326196924</v>
+        <v>326771202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2815,40 +2856,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>734</v>
+        <v>1388</v>
       </c>
       <c r="H29" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R0Q3R</t>
+          <t>UJ56J</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>326218704</v>
+        <v>326809475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2857,40 +2898,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DDJHB</t>
+          <t>09SKZ</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>326248685</v>
+        <v>326799637</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2899,40 +2940,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1230</v>
+        <v>615</v>
       </c>
       <c r="H31" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="I31" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UMQ7H</t>
+          <t>CL8II</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>326154984</v>
+        <v>326749961</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2950,31 +2991,31 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>703</v>
+        <v>347</v>
       </c>
       <c r="H32" t="n">
-        <v>180</v>
+        <v>66</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>180</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RKBXJ</t>
+          <t>SFH19</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>326158069</v>
+        <v>326768420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2992,31 +3033,31 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>532</v>
+        <v>649</v>
       </c>
       <c r="H33" t="n">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>107</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>O7EBF</t>
+          <t>MCSPM</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>326163252</v>
+        <v>326847193</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3025,40 +3066,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Вінстона Черчиля</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>567</v>
+        <v>628</v>
       </c>
       <c r="H34" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GIM0N</t>
+          <t>9TES8</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>326170567</v>
+        <v>326790701</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3067,40 +3108,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Олександра Олеся</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>998</v>
+        <v>661</v>
       </c>
       <c r="H35" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WKK2M</t>
+          <t>NE1NW</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>326170966</v>
+        <v>326744145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3109,40 +3150,40 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>825</v>
+        <v>647</v>
       </c>
       <c r="H36" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>147</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6HV0P</t>
+          <t>HF077</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>326217236</v>
+        <v>326883220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3151,7 +3192,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>вул. Олександра Олеся</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3160,31 +3201,31 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>684</v>
+        <v>1251</v>
       </c>
       <c r="H37" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="I37" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OXSUB</t>
+          <t>99UKP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>326324795</v>
+        <v>326846098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3193,40 +3234,40 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>600</v>
+        <v>447</v>
       </c>
       <c r="H38" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="I38" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>YKXVN</t>
+          <t>BO14C</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>326343015</v>
+        <v>327175694</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3244,31 +3285,31 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>563</v>
+        <v>700</v>
       </c>
       <c r="H39" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J39" t="n">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N87KG</t>
+          <t>RJZK8</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>326357818</v>
+        <v>327163139</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3277,7 +3318,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3286,31 +3327,31 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>669</v>
+        <v>782</v>
       </c>
       <c r="H40" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q2INM</t>
+          <t>GKJ8Z</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>326380438</v>
+        <v>327285082</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3328,31 +3369,31 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>713</v>
+        <v>1110</v>
       </c>
       <c r="H41" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="I41" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BVSI1</t>
+          <t>70IPJ</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>326386106</v>
+        <v>327177314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3361,40 +3402,40 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1362</v>
+        <v>602</v>
       </c>
       <c r="H42" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="I42" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>131</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SBE4S</t>
+          <t>C158E</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>326407741</v>
+        <v>327166814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3403,40 +3444,40 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>749</v>
+        <v>687</v>
       </c>
       <c r="H43" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LRTT2</t>
+          <t>6LCV5</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>326413258</v>
+        <v>327250306</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3445,7 +3486,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3454,31 +3495,31 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>610</v>
+        <v>998</v>
       </c>
       <c r="H44" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="I44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J44" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H7FKW</t>
+          <t>U7877</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>326313204</v>
+        <v>327249750</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3487,25 +3528,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1132</v>
+        <v>1382</v>
       </c>
       <c r="H45" t="n">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="I45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J45" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46">
@@ -3516,11 +3557,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21MSS</t>
+          <t>LTJWV</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>326316659</v>
+        <v>326336819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3529,7 +3570,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3538,16 +3579,16 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>996</v>
+        <v>717</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -3558,11 +3599,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QICDE</t>
+          <t>H7FKW</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>326348240</v>
+        <v>326313204</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3580,16 +3621,16 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>590</v>
+        <v>1132</v>
       </c>
       <c r="H47" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J47" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48">
@@ -3600,11 +3641,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R9Q00</t>
+          <t>WNR6Z</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>326371586</v>
+        <v>326435493</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3613,7 +3654,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>вул. Олександра Олеся</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3622,16 +3663,16 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>362</v>
+        <v>709</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J48" t="n">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
@@ -3642,11 +3683,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LTJWV</t>
+          <t>OXSUB</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>326336819</v>
+        <v>326324795</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -3655,7 +3696,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3664,16 +3705,16 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>717</v>
+        <v>600</v>
       </c>
       <c r="H49" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J49" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50">
@@ -3684,11 +3725,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FKE1W</t>
+          <t>SBE4S</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>326355483</v>
+        <v>326407741</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -3697,7 +3738,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3706,16 +3747,16 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>392</v>
+        <v>749</v>
       </c>
       <c r="H50" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
@@ -3726,11 +3767,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LJO3V</t>
+          <t>Z3UEN</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>326398218</v>
+        <v>326330234</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -3739,7 +3780,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3748,16 +3789,16 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>582</v>
+        <v>1355</v>
       </c>
       <c r="H51" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J51" t="n">
-        <v>60</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52">
@@ -3768,11 +3809,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4E6P8</t>
+          <t>68KPB</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>326403150</v>
+        <v>326402507</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -3781,7 +3822,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3790,16 +3831,16 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>461</v>
+        <v>596</v>
       </c>
       <c r="H52" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
@@ -3810,11 +3851,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KFET7</t>
+          <t>FKE1W</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>326432502</v>
+        <v>326355483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -3832,16 +3873,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1920</v>
+        <v>392</v>
       </c>
       <c r="H53" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="I53" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -3852,11 +3893,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Z3UEN</t>
+          <t>PTIUE</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>326330234</v>
+        <v>326316803</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3865,25 +3906,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1355</v>
+        <v>1045</v>
       </c>
       <c r="H54" t="n">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="I54" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>198</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
@@ -3894,11 +3935,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DCD77</t>
+          <t>Q2INM</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>326412770</v>
+        <v>326380438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3907,7 +3948,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3916,16 +3957,16 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>934</v>
+        <v>713</v>
       </c>
       <c r="H55" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I55" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J55" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56">
@@ -3936,11 +3977,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PTIUE</t>
+          <t>N87KG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>326316803</v>
+        <v>326357818</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3949,25 +3990,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1045</v>
+        <v>669</v>
       </c>
       <c r="H56" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
@@ -3978,11 +4019,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HHPCC</t>
+          <t>QWQ0T</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>326385372</v>
+        <v>326322469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -3991,25 +4032,25 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>658</v>
+        <v>590</v>
       </c>
       <c r="H57" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58">
@@ -4020,11 +4061,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>68KPB</t>
+          <t>DCD77</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>326402507</v>
+        <v>326412770</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4033,7 +4074,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4042,31 +4083,31 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>596</v>
+        <v>934</v>
       </c>
       <c r="H58" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="J58" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3A82H</t>
+          <t>RKLX5</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>326404789</v>
+        <v>326649915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4075,7 +4116,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4084,31 +4125,31 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>807</v>
+        <v>1705</v>
       </c>
       <c r="H59" t="n">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="I59" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>O54U7</t>
+          <t>XD1OL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>326438143</v>
+        <v>326589586</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4117,7 +4158,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4126,31 +4167,31 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>576</v>
+        <v>819</v>
       </c>
       <c r="H60" t="n">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>69</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0E4KM</t>
+          <t>Q3AHZ</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>326345917</v>
+        <v>326521657</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4159,40 +4200,40 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>859</v>
+        <v>437</v>
       </c>
       <c r="H61" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>L2R3U</t>
+          <t>TMLCS</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>326364608</v>
+        <v>326518276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4201,40 +4242,40 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="H62" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>104</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01MP9</t>
+          <t>5VNKX</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>326412910</v>
+        <v>326590027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4243,40 +4284,40 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>685</v>
+        <v>802</v>
       </c>
       <c r="H63" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QWQ0T</t>
+          <t>AJF7E</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>326322469</v>
+        <v>326602412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4285,40 +4326,40 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>590</v>
+        <v>781</v>
       </c>
       <c r="H64" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J64" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K6UIC</t>
+          <t>MQNAP</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>326368777</v>
+        <v>326539900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4327,49 +4368,49 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>660</v>
+        <v>543</v>
       </c>
       <c r="H65" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I65" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9VC89</t>
+          <t>L7PKJ</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>326454352</v>
+        <v>326553697</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Європіано</t>
+          <t>Муза</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>вул. Героїв полку «Азов»</t>
+          <t>вул. Вінстона Черчиля</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4378,31 +4419,31 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3575</v>
+        <v>1314</v>
       </c>
       <c r="H66" t="n">
-        <v>435</v>
+        <v>16</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>435</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WNR6Z</t>
+          <t>ADYNV</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>326435493</v>
+        <v>326523459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4411,25 +4452,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>вул. Олександра Олеся</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="H67" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="I67" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68">
@@ -4440,11 +4481,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4BL76</t>
+          <t>0JHMY</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>326584909</v>
+        <v>326587664</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4453,25 +4494,25 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>738</v>
+        <v>971</v>
       </c>
       <c r="H68" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>57</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69">
@@ -4482,11 +4523,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5VNKX</t>
+          <t>RY711</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>326590027</v>
+        <v>326528034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -4495,7 +4536,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4504,16 +4545,16 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>802</v>
+        <v>885</v>
       </c>
       <c r="H69" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70">
@@ -4524,11 +4565,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RY711</t>
+          <t>E8Y1H</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>326528034</v>
+        <v>326606929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -4537,7 +4578,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4546,16 +4587,16 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>885</v>
+        <v>1099</v>
       </c>
       <c r="H70" t="n">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71">
@@ -4608,20 +4649,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MQNAP</t>
+          <t>Z9YPD</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>326539900</v>
+        <v>326667556</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Муза</t>
+          <t>Європіано</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4630,31 +4671,31 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>543</v>
+        <v>741</v>
       </c>
       <c r="H72" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>QVIBW</t>
+          <t>0K0GD</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>326637654</v>
+        <v>327474686</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -4672,31 +4713,31 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1306</v>
+        <v>626</v>
       </c>
       <c r="H73" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>L7PKJ</t>
+          <t>S0J9B</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>326553697</v>
+        <v>327542203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -4705,7 +4746,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчиля</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4714,31 +4755,31 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1314</v>
+        <v>640</v>
       </c>
       <c r="H74" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J74" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>XLVNZ</t>
+          <t>Y0R1L</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>326517837</v>
+        <v>327403297</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -4747,7 +4788,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4756,31 +4797,31 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>572</v>
+        <v>1462</v>
       </c>
       <c r="H75" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J75" t="n">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>XD1OL</t>
+          <t>BYDOL</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>326589586</v>
+        <v>327444393</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -4789,40 +4830,40 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>819</v>
+        <v>913</v>
       </c>
       <c r="H76" t="n">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J76" t="n">
-        <v>133</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H673W</t>
+          <t>N69CG</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>326536127</v>
+        <v>327452943</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -4831,7 +4872,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4840,31 +4881,31 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>727</v>
+        <v>976</v>
       </c>
       <c r="H77" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7PBFQ</t>
+          <t>HLKBT</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>326574758</v>
+        <v>327467715</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -4882,31 +4923,31 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>921</v>
+        <v>1185</v>
       </c>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J78" t="n">
-        <v>12</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AJF7E</t>
+          <t>PS82H</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>326602412</v>
+        <v>327549848</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -4915,40 +4956,40 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>781</v>
+        <v>378</v>
       </c>
       <c r="H79" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I79" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TMLCS</t>
+          <t>LO3LP</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>326518276</v>
+        <v>327497176</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -4957,40 +4998,40 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>522</v>
+        <v>629</v>
       </c>
       <c r="H80" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J80" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>O9RB3</t>
+          <t>4M43D</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>326603092</v>
+        <v>326795330</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -4999,7 +5040,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5008,31 +5049,31 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>988</v>
+        <v>672</v>
       </c>
       <c r="H81" t="n">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>174</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4WTFZ</t>
+          <t>0BZ4L</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>326626431</v>
+        <v>326747343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5041,40 +5082,40 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1594</v>
+        <v>837</v>
       </c>
       <c r="H82" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RKLX5</t>
+          <t>HF8HH</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>326649915</v>
+        <v>326766401</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -5083,40 +5124,40 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1705</v>
+        <v>595</v>
       </c>
       <c r="H83" t="n">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>256</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2IYZY</t>
+          <t>JHK0F</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>326646499</v>
+        <v>326733408</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -5125,7 +5166,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5134,31 +5175,31 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1017</v>
+        <v>1639</v>
       </c>
       <c r="H84" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IEWBS</t>
+          <t>LV65L</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>326649937</v>
+        <v>326741101</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -5167,40 +5208,40 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>798</v>
+        <v>356</v>
       </c>
       <c r="H85" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Q3AHZ</t>
+          <t>5AZYV</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>326521657</v>
+        <v>326768987</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -5209,7 +5250,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5218,31 +5259,31 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>437</v>
+        <v>527</v>
       </c>
       <c r="H86" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>E8Y1H</t>
+          <t>XXCC6</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>326606929</v>
+        <v>326788325</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -5251,7 +5292,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5260,31 +5301,31 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1099</v>
+        <v>578</v>
       </c>
       <c r="H87" t="n">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>166</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0JHMY</t>
+          <t>4ZTJ8</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>326587664</v>
+        <v>326785851</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -5293,40 +5334,40 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>971</v>
+        <v>599</v>
       </c>
       <c r="H88" t="n">
-        <v>167</v>
+        <v>43</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>167</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VADPS</t>
+          <t>CVUG7</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>326615012</v>
+        <v>326881563</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -5335,40 +5376,40 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>930</v>
+        <v>953</v>
       </c>
       <c r="H89" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ADYNV</t>
+          <t>RCPPW</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>326523459</v>
+        <v>327108153</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -5377,40 +5418,40 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>703</v>
+        <v>950</v>
       </c>
       <c r="H90" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>24OXW</t>
+          <t>U9G35</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>326648547</v>
+        <v>327067553</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -5419,49 +5460,49 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1368</v>
+        <v>1618</v>
       </c>
       <c r="H91" t="n">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>206</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Z9YPD</t>
+          <t>ICKJK</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>326667556</v>
+        <v>326973930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Європіано</t>
+          <t>Муза</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5470,31 +5511,31 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>741</v>
+        <v>559</v>
       </c>
       <c r="H92" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UJ56J</t>
+          <t>BJB2T</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>326809475</v>
+        <v>327017430</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -5503,7 +5544,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5512,31 +5553,31 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>590</v>
+        <v>683</v>
       </c>
       <c r="H93" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4ZTJ8</t>
+          <t>U9TZG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>326785851</v>
+        <v>327030473</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -5545,7 +5586,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5554,31 +5595,31 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>599</v>
+        <v>494</v>
       </c>
       <c r="H94" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HF077</t>
+          <t>A0PBS</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>326883220</v>
+        <v>326983969</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -5587,40 +5628,40 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1251</v>
+        <v>833</v>
       </c>
       <c r="H95" t="n">
-        <v>42</v>
+        <v>205</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>42</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MCSPM</t>
+          <t>90FNI</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>326847193</v>
+        <v>326975614</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5629,7 +5670,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчиля</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5638,31 +5679,31 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>628</v>
+        <v>975</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>50</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5AZYV</t>
+          <t>UIRVH</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>326768987</v>
+        <v>327082689</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -5671,40 +5712,40 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="H97" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>09SKZ</t>
+          <t>S9L3L</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>326799637</v>
+        <v>326940540</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -5713,40 +5754,40 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>615</v>
+        <v>688</v>
       </c>
       <c r="H98" t="n">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JHK0F</t>
+          <t>WSO1T</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>326733408</v>
+        <v>327004900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -5755,7 +5796,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5764,31 +5805,31 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1639</v>
+        <v>1126</v>
       </c>
       <c r="H99" t="n">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="I99" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J99" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LV65L</t>
+          <t>B33J2</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>326741101</v>
+        <v>327097763</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -5797,7 +5838,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5806,31 +5847,31 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>356</v>
+        <v>897</v>
       </c>
       <c r="H100" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KDZDR</t>
+          <t>8WOE8</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>326755831</v>
+        <v>326938519</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -5839,40 +5880,40 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2008</v>
+        <v>788</v>
       </c>
       <c r="H101" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>223</v>
+        <v>195</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>55HJ4</t>
+          <t>SK1LD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>326771202</v>
+        <v>327396794</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -5881,7 +5922,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5890,31 +5931,31 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1388</v>
+        <v>522</v>
       </c>
       <c r="H102" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I102" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>XXCC6</t>
+          <t>ZHKXJ</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>326788325</v>
+        <v>327382387</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -5923,7 +5964,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5932,31 +5973,31 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>578</v>
+        <v>626</v>
       </c>
       <c r="H103" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J103" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4M43D</t>
+          <t>IJ041</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>326795330</v>
+        <v>327436087</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -5965,7 +6006,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5974,31 +6015,31 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>672</v>
+        <v>990</v>
       </c>
       <c r="H104" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J104" t="n">
-        <v>24</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVUG7</t>
+          <t>SF7FE</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>326881563</v>
+        <v>327495435</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -6007,40 +6048,40 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>953</v>
+        <v>304</v>
       </c>
       <c r="H105" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J105" t="n">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0BZ4L</t>
+          <t>IH5U8</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>326747343</v>
+        <v>327422361</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -6049,40 +6090,40 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>837</v>
+        <v>1316</v>
       </c>
       <c r="H106" t="n">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J106" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CL8II</t>
+          <t>PLC11</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>326749961</v>
+        <v>327478196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -6091,40 +6132,40 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>347</v>
+        <v>533</v>
       </c>
       <c r="H107" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HF8HH</t>
+          <t>5K291</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>326766401</v>
+        <v>327551970</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -6133,40 +6174,40 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>595</v>
+        <v>1151</v>
       </c>
       <c r="H108" t="n">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J108" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SFH19</t>
+          <t>4XI2Z</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>326768420</v>
+        <v>327479371</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -6184,31 +6225,31 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>649</v>
+        <v>593</v>
       </c>
       <c r="H109" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>99UKP</t>
+          <t>4EW06</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>326846098</v>
+        <v>327450885</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -6226,31 +6267,31 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>447</v>
+        <v>873</v>
       </c>
       <c r="H110" t="n">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>77</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NE1NW</t>
+          <t>3DB4N</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>326744145</v>
+        <v>327475237</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -6259,40 +6300,40 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>647</v>
+        <v>961</v>
       </c>
       <c r="H111" t="n">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>61</v>
+        <v>177</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9TES8</t>
+          <t>AVGDK</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>326790701</v>
+        <v>327489739</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -6301,7 +6342,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>вул. Олександра Олеся</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6310,31 +6351,31 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>661</v>
+        <v>999</v>
       </c>
       <c r="H112" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J112" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OFJI6</t>
+          <t>TWG51</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>326961338</v>
+        <v>327482931</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -6343,7 +6384,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6352,31 +6393,31 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1148</v>
+        <v>1224</v>
       </c>
       <c r="H113" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="J113" t="n">
-        <v>34</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0ZFDW</t>
+          <t>STJRA</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>326972974</v>
+        <v>327212596</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -6385,7 +6426,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6394,31 +6435,31 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>1828</v>
+        <v>1486</v>
       </c>
       <c r="H114" t="n">
-        <v>209</v>
+        <v>63</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J114" t="n">
-        <v>209</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>90FNI</t>
+          <t>2MZLE</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>326975614</v>
+        <v>327266396</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -6427,7 +6468,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Вінстона Черчиля</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6436,31 +6477,31 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>975</v>
+        <v>1120</v>
       </c>
       <c r="H115" t="n">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J115" t="n">
-        <v>141</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TUAP4</t>
+          <t>V2ATM</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>327001613</v>
+        <v>327308392</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -6478,31 +6519,31 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>729</v>
+        <v>868</v>
       </c>
       <c r="H116" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J116" t="n">
-        <v>54</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RCPPW</t>
+          <t>O6F1S</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>327108153</v>
+        <v>327219977</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -6511,7 +6552,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6520,31 +6561,31 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>950</v>
+        <v>615</v>
       </c>
       <c r="H117" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J117" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>A0BVY</t>
+          <t>LQ8PG</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>326994940</v>
+        <v>327209933</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -6553,40 +6594,40 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>640</v>
+        <v>891</v>
       </c>
       <c r="H118" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ICKJK</t>
+          <t>B0YLO</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>326973930</v>
+        <v>327195221</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -6595,7 +6636,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6604,31 +6645,31 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="H119" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>W5ZDC</t>
+          <t>4I83M</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>327043373</v>
+        <v>327210836</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -6637,7 +6678,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6646,31 +6687,31 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2079</v>
+        <v>990</v>
       </c>
       <c r="H120" t="n">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J120" t="n">
-        <v>154</v>
+        <v>93</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>B33J2</t>
+          <t>CWOWV</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>327097763</v>
+        <v>327237362</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -6679,40 +6720,40 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>897</v>
+        <v>1710</v>
       </c>
       <c r="H121" t="n">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>81</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>8WOE8</t>
+          <t>QQ92T</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>326938519</v>
+        <v>327275023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -6730,31 +6771,31 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>788</v>
+        <v>699</v>
       </c>
       <c r="H122" t="n">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J122" t="n">
-        <v>195</v>
+        <v>76</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>08AYA</t>
+          <t>MXR2U</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>327003469</v>
+        <v>327313385</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -6763,7 +6804,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6772,31 +6813,31 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1345</v>
+        <v>801</v>
       </c>
       <c r="H123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BJB2T</t>
+          <t>2LV9B</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>327017430</v>
+        <v>327256927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -6805,7 +6846,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6814,31 +6855,31 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>683</v>
+        <v>570</v>
       </c>
       <c r="H124" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J124" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>U9TZG</t>
+          <t>O8NQT</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>327030473</v>
+        <v>327288888</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -6847,40 +6888,40 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Пекарська</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>494</v>
+        <v>842</v>
       </c>
       <c r="H125" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J125" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>U9G35</t>
+          <t>X51QC</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>327067553</v>
+        <v>327288528</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -6889,7 +6930,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6898,31 +6939,31 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1618</v>
+        <v>460</v>
       </c>
       <c r="H126" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J126" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LMP88</t>
+          <t>P2RMM</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>327083950</v>
+        <v>327362914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -6931,7 +6972,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6940,31 +6981,31 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1261</v>
+        <v>367</v>
       </c>
       <c r="H127" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>YC61U</t>
+          <t>01MP9</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>326977076</v>
+        <v>326412910</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -6973,40 +7014,40 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>986</v>
+        <v>685</v>
       </c>
       <c r="H128" t="n">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>12</v>
+        <v>136</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>WSO1T</t>
+          <t>LRTT2</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>327004900</v>
+        <v>326413258</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -7015,40 +7056,40 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>1126</v>
+        <v>610</v>
       </c>
       <c r="H129" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="I129" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="J129" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S9L3L</t>
+          <t>L2R3U</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>326940540</v>
+        <v>326364608</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -7057,82 +7098,82 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>688</v>
+        <v>587</v>
       </c>
       <c r="H130" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>A0PBS</t>
+          <t>9VC89</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>326983969</v>
+        <v>326454352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Муза</t>
+          <t>Європіано</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>833</v>
+        <v>3575</v>
       </c>
       <c r="H131" t="n">
-        <v>205</v>
+        <v>435</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>205</v>
+        <v>435</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1AUE9</t>
+          <t>R9Q00</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>327051488</v>
+        <v>326371586</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -7141,40 +7182,40 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>538</v>
+        <v>362</v>
       </c>
       <c r="H132" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J132" t="n">
-        <v>92</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7MYE5</t>
+          <t>K6UIC</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>327069057</v>
+        <v>326368777</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -7192,31 +7233,31 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1314</v>
+        <v>660</v>
       </c>
       <c r="H133" t="n">
-        <v>193</v>
+        <v>37</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J133" t="n">
-        <v>193</v>
+        <v>74</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>UIRVH</t>
+          <t>KFET7</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>327082689</v>
+        <v>326432502</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -7225,40 +7266,40 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>538</v>
+        <v>1920</v>
       </c>
       <c r="H134" t="n">
         <v>55</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J134" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BO14C</t>
+          <t>YKXVN</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>327175694</v>
+        <v>326343015</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -7276,31 +7317,31 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>700</v>
+        <v>563</v>
       </c>
       <c r="H135" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="I135" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>4I83M</t>
+          <t>4E6P8</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>327210836</v>
+        <v>326403150</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -7309,7 +7350,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7318,31 +7359,31 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>990</v>
+        <v>461</v>
       </c>
       <c r="H136" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="I136" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>93</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GKJ8Z</t>
+          <t>BVSI1</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>327285082</v>
+        <v>326386106</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -7360,31 +7401,31 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1110</v>
+        <v>1362</v>
       </c>
       <c r="H137" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J137" t="n">
-        <v>82</v>
+        <v>131</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>X51QC</t>
+          <t>LJO3V</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>327288528</v>
+        <v>326398218</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -7393,7 +7434,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7402,31 +7443,31 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>460</v>
+        <v>582</v>
       </c>
       <c r="H138" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="I138" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>V2ATM</t>
+          <t>0E4KM</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>327308392</v>
+        <v>326345917</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -7435,40 +7476,40 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="H139" t="n">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="I139" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RJZK8</t>
+          <t>QICDE</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>327163139</v>
+        <v>326348240</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -7486,31 +7527,31 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>782</v>
+        <v>590</v>
       </c>
       <c r="H140" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J140" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0YLO</t>
+          <t>21MSS</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>327195221</v>
+        <v>326316659</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -7528,31 +7569,31 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>566</v>
+        <v>996</v>
       </c>
       <c r="H141" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J141" t="n">
-        <v>61</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>6LCV5</t>
+          <t>3A82H</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>327250306</v>
+        <v>326404789</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -7561,7 +7602,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7570,31 +7611,31 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>998</v>
+        <v>807</v>
       </c>
       <c r="H142" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="I142" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J142" t="n">
-        <v>107</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2LV9B</t>
+          <t>HHPCC</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>327256927</v>
+        <v>326385372</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -7603,7 +7644,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7612,31 +7653,31 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="H143" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="I143" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2MZLE</t>
+          <t>O54U7</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>327266396</v>
+        <v>326438143</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -7645,7 +7686,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>вул. Вінстона Черчиля</t>
+          <t>на Бастіонній</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7654,31 +7695,31 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1120</v>
+        <v>576</v>
       </c>
       <c r="H144" t="n">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I144" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>QQ92T</t>
+          <t>KBASA</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>327275023</v>
+        <v>326116108</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -7687,40 +7728,40 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>699</v>
+        <v>978</v>
       </c>
       <c r="H145" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="I145" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J145" t="n">
-        <v>76</v>
+        <v>149</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>O8NQT</t>
+          <t>YTLJ1</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>327288888</v>
+        <v>326208615</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -7729,40 +7770,40 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Пекарська</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>842</v>
+        <v>655</v>
       </c>
       <c r="H146" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I146" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J146" t="n">
-        <v>99</v>
+        <v>129</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>70IPJ</t>
+          <t>PIV31</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>327177314</v>
+        <v>326127631</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -7771,7 +7812,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7780,31 +7821,31 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>602</v>
+        <v>1030</v>
       </c>
       <c r="H147" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J147" t="n">
-        <v>37</v>
+        <v>143</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MXR2U</t>
+          <t>Z2W1A</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>327313385</v>
+        <v>326175314</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -7813,40 +7854,40 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>801</v>
+        <v>776</v>
       </c>
       <c r="H148" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J148" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>STJRA</t>
+          <t>R0Q3R</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>327212596</v>
+        <v>326218704</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -7855,40 +7896,40 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1486</v>
+        <v>612</v>
       </c>
       <c r="H149" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I149" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>O6F1S</t>
+          <t>RKBXJ</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>327219977</v>
+        <v>326158069</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -7897,40 +7938,40 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>615</v>
+        <v>532</v>
       </c>
       <c r="H150" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="I150" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>C158E</t>
+          <t>VKR08</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>327166814</v>
+        <v>326262272</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -7939,40 +7980,40 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>687</v>
+        <v>896</v>
       </c>
       <c r="H151" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J151" t="n">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CWOWV</t>
+          <t>0N35U</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>327237362</v>
+        <v>326130893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -7981,40 +8022,40 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1710</v>
+        <v>887</v>
       </c>
       <c r="H152" t="n">
-        <v>424</v>
+        <v>142</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J152" t="n">
-        <v>424</v>
+        <v>154</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LQ8PG</t>
+          <t>SB6QE</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>327209933</v>
+        <v>326246119</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -8023,40 +8064,40 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>891</v>
+        <v>611</v>
       </c>
       <c r="H153" t="n">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J153" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>U7877</t>
+          <t>BN5SD</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>327249750</v>
+        <v>326116606</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -8065,40 +8106,40 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>пров. Олекси Тихого</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Irpin</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1382</v>
+        <v>436</v>
       </c>
       <c r="H154" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="I154" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="J154" t="n">
-        <v>155</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ZHKXJ</t>
+          <t>E8TJX</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>327382387</v>
+        <v>326255976</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -8107,7 +8148,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8116,31 +8157,31 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="H155" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I155" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J155" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IH5U8</t>
+          <t>6HV0P</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>327422361</v>
+        <v>326217236</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -8149,7 +8190,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>вул. Олександра Олеся</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8158,31 +8199,31 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1316</v>
+        <v>684</v>
       </c>
       <c r="H156" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="I156" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="J156" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>N69CG</t>
+          <t>E98NJ</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>327452943</v>
+        <v>326187954</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -8200,31 +8241,31 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>976</v>
+        <v>705</v>
       </c>
       <c r="H157" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I157" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J157" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5K291</t>
+          <t>KSOM5</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>327551970</v>
+        <v>326232732</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -8233,22 +8274,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>вул. Саксаганського</t>
+          <t>Чорновола</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1151</v>
+        <v>1205</v>
       </c>
       <c r="H158" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="I158" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="J158" t="n">
         <v>125</v>
@@ -8257,16 +8298,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Y0R1L</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>327403297</v>
+        <v>326236427</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -8275,7 +8316,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>вул. Вінстона Черчиля</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8284,31 +8325,31 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1462</v>
+        <v>862</v>
       </c>
       <c r="H159" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I159" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="J159" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0K0GD</t>
+          <t>GIM0N</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>327474686</v>
+        <v>326170567</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -8317,40 +8358,40 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>626</v>
+        <v>998</v>
       </c>
       <c r="H160" t="n">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>67</v>
+        <v>164</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PLC11</t>
+          <t>UMQ7H</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>327478196</v>
+        <v>326154984</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -8359,40 +8400,40 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>533</v>
+        <v>703</v>
       </c>
       <c r="H161" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PS82H</t>
+          <t>PUPBI</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>327549848</v>
+        <v>326216591</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -8401,7 +8442,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>вул. Срібнокільська</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8410,7 +8451,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>378</v>
+        <v>670</v>
       </c>
       <c r="H162" t="n">
         <v>19</v>
@@ -8425,16 +8466,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>P2RMM</t>
+          <t>8C9E2</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>327362914</v>
+        <v>326141475</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -8443,7 +8484,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>вул. Героїв Полку Азов</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8452,31 +8493,31 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>367</v>
+        <v>570</v>
       </c>
       <c r="H163" t="n">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>41</v>
+        <v>130</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HLKBT</t>
+          <t>00JZX</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>327467715</v>
+        <v>326196924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -8485,40 +8526,40 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1185</v>
+        <v>734</v>
       </c>
       <c r="H164" t="n">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="I164" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="J164" t="n">
-        <v>164</v>
+        <v>66</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AVGDK</t>
+          <t>IEWBS</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>327489739</v>
+        <v>326649937</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -8527,40 +8568,40 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>вул. Гарматна</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>999</v>
+        <v>798</v>
       </c>
       <c r="H165" t="n">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I165" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>141</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SK1LD</t>
+          <t>VADPS</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>327396794</v>
+        <v>326615012</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -8569,40 +8610,40 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>Рівне</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kyiv</t>
+          <t>Rivne</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>522</v>
+        <v>930</v>
       </c>
       <c r="H166" t="n">
-        <v>22</v>
+        <v>173</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>22</v>
+        <v>173</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>IJ041</t>
+          <t>4BL76</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>327436087</v>
+        <v>326584909</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -8611,7 +8652,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Саксаганського</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8620,31 +8661,31 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>990</v>
+        <v>738</v>
       </c>
       <c r="H167" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="I167" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TWG51</t>
+          <t>QVIBW</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>327482931</v>
+        <v>326637654</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -8653,7 +8694,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>провулок Коломийський</t>
+          <t>вул. Срібнокільська</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8662,31 +8703,31 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1224</v>
+        <v>1306</v>
       </c>
       <c r="H168" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="I168" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>142</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LO3LP</t>
+          <t>XLVNZ</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>327497176</v>
+        <v>326517837</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -8695,40 +8736,40 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Чорновола</t>
+          <t>вул. Героїв Полку Азов</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>629</v>
+        <v>572</v>
       </c>
       <c r="H169" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="I169" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>108</v>
+        <v>43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BYDOL</t>
+          <t>7PBFQ</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>327444393</v>
+        <v>326574758</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -8737,40 +8778,40 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="H170" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I170" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SF7FE</t>
+          <t>H673W</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>327495435</v>
+        <v>326536127</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -8779,40 +8820,40 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Федьковича</t>
+          <t>вул. Гарматна</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lviv</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>304</v>
+        <v>727</v>
       </c>
       <c r="H171" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="I171" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S0J9B</t>
+          <t>4WTFZ</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>327542203</v>
+        <v>326626431</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -8821,7 +8862,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>на Бастіонній</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8830,31 +8871,31 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>640</v>
+        <v>1594</v>
       </c>
       <c r="H172" t="n">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="I172" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J172" t="n">
-        <v>68</v>
+        <v>151</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>4EW06</t>
+          <t>O9RB3</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>327450885</v>
+        <v>326603092</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -8863,40 +8904,40 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>пров. Коломийський</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Kyiv</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>873</v>
+        <v>988</v>
       </c>
       <c r="H173" t="n">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J173" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3DB4N</t>
+          <t>2IYZY</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>327475237</v>
+        <v>326646499</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -8905,40 +8946,40 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>Федьковича</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Lviv</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>961</v>
+        <v>1017</v>
       </c>
       <c r="H174" t="n">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>177</v>
+        <v>45</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>4XI2Z</t>
+          <t>24OXW</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>327479371</v>
+        <v>326648547</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -8947,25 +8988,25 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Рівне</t>
+          <t>пров. Олекси Тихого</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rivne</t>
+          <t>Irpin</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>593</v>
+        <v>1368</v>
       </c>
       <c r="H175" t="n">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>109</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
